--- a/www/flightdata/xlsx/eoss-309.xlsx
+++ b/www/flightdata/xlsx/eoss-309.xlsx
@@ -3369,7 +3369,7 @@
         <v>30373.62</v>
       </c>
       <c r="I2">
-        <v>573</v>
+        <v>425</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
